--- a/data/DIM_TAMBUDGET.xlsx
+++ b/data/DIM_TAMBUDGET.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://freightways-my.sharepoint.com/personal/tuyet_pham_dxmail_co_nz/Documents/Desktop/PROJECTS/Sales Dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb76a992d3c9d4c0/Desktop/Sales Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="11_F25DC773A252ABDACC1048F1995C62D85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{997F5A7B-FA68-456A-A379-F2E4BB76B21F}"/>
+  <xr:revisionPtr revIDLastSave="177" documentId="11_F25DC773A252ABDACC1048F1995C62D85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03D6941C-797F-4137-A244-02429112134E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,21 +41,6 @@
     <t>ID</t>
   </si>
   <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>TAM1</t>
-  </si>
-  <si>
-    <t>TAM2</t>
-  </si>
-  <si>
-    <t>TAM3</t>
-  </si>
-  <si>
-    <t>TAM4</t>
-  </si>
-  <si>
     <t>MONTH</t>
   </si>
   <si>
@@ -63,6 +48,21 @@
   </si>
   <si>
     <t>BUDGET</t>
+  </si>
+  <si>
+    <t>REP1</t>
+  </si>
+  <si>
+    <t>REP2</t>
+  </si>
+  <si>
+    <t>REP3</t>
+  </si>
+  <si>
+    <t>REP4</t>
+  </si>
+  <si>
+    <t>TAM</t>
   </si>
 </sst>
 </file>
@@ -420,35 +420,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E121"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -460,12 +460,12 @@
         <v>582537.00799999991</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -477,12 +477,12 @@
         <v>654868.08649999998</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -494,12 +494,12 @@
         <v>797329.20099999988</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -511,12 +511,12 @@
         <v>552633.56949999998</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -528,12 +528,12 @@
         <v>657447.47899999993</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -545,12 +545,12 @@
         <v>799199.96349999995</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -562,12 +562,12 @@
         <v>661564.65149999992</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -579,12 +579,12 @@
         <v>694440.52949999995</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -596,12 +596,12 @@
         <v>882902.32250000001</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -613,12 +613,12 @@
         <v>620206.94849999994</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -630,12 +630,12 @@
         <v>709368.89799999993</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -647,12 +647,12 @@
         <v>728624.29099999985</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -664,12 +664,12 @@
         <v>542194.65149999992</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -681,12 +681,12 @@
         <v>521891.70049999998</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -698,12 +698,12 @@
         <v>700494.55499999993</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C17">
         <v>4</v>
@@ -715,12 +715,12 @@
         <v>563149.85950000002</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -732,12 +732,12 @@
         <v>575007.26799999992</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -749,12 +749,12 @@
         <v>728841.34199999995</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>7</v>
@@ -766,12 +766,12 @@
         <v>614557.21699999995</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C21">
         <v>8</v>
@@ -783,12 +783,12 @@
         <v>713123.79749999999</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>9</v>
@@ -800,12 +800,12 @@
         <v>1143885.9099999999</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -817,12 +817,12 @@
         <v>648287.42999999993</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>11</v>
@@ -834,12 +834,12 @@
         <v>656240.02499999991</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>12</v>
@@ -851,12 +851,12 @@
         <v>830959.01899999997</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -868,12 +868,12 @@
         <v>500377.85699999996</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -885,12 +885,12 @@
         <v>651203.87599999993</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -902,12 +902,12 @@
         <v>869339.65949999995</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>4</v>
@@ -919,12 +919,12 @@
         <v>569400.58100000001</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -936,12 +936,12 @@
         <v>699794.40049999999</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C31">
         <v>6</v>
@@ -953,12 +953,12 @@
         <v>834302.74749999994</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>7</v>
@@ -970,12 +970,12 @@
         <v>687764.36549999996</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C33">
         <v>8</v>
@@ -987,12 +987,12 @@
         <v>770244.99899999995</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>9</v>
@@ -1004,12 +1004,12 @@
         <v>761492.83200000005</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C35">
         <v>10</v>
@@ -1021,12 +1021,12 @@
         <v>679340.73049999983</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C36">
         <v>11</v>
@@ -1038,12 +1038,12 @@
         <v>757416.07050000003</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C37">
         <v>12</v>
@@ -1055,12 +1055,12 @@
         <v>804767.723</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1072,12 +1072,12 @@
         <v>414797.9045</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -1089,12 +1089,12 @@
         <v>531217.09649999999</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -1106,12 +1106,12 @@
         <v>661341.67799999996</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C41">
         <v>4</v>
@@ -1123,12 +1123,12 @@
         <v>588442.62599999993</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C42">
         <v>5</v>
@@ -1140,12 +1140,12 @@
         <v>528540.40249999997</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C43">
         <v>6</v>
@@ -1157,12 +1157,12 @@
         <v>693135.8544999999</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C44">
         <v>7</v>
@@ -1174,12 +1174,12 @@
         <v>518672.53999999992</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C45">
         <v>8</v>
@@ -1191,12 +1191,12 @@
         <v>679348.20549999992</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C46">
         <v>9</v>
@@ -1208,12 +1208,12 @@
         <v>765394.09199999995</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C47">
         <v>10</v>
@@ -1225,12 +1225,12 @@
         <v>658911.33699999994</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C48">
         <v>11</v>
@@ -1242,12 +1242,12 @@
         <v>697444.65149999992</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C49">
         <v>12</v>
@@ -1259,12 +1259,12 @@
         <v>837874.02649999992</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -1276,12 +1276,12 @@
         <v>546467.35</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -1293,12 +1293,12 @@
         <v>648087.1</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -1310,12 +1310,12 @@
         <v>741740.8</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C53">
         <v>4</v>
@@ -1327,12 +1327,12 @@
         <v>607427.69999999995</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C54">
         <v>5</v>
@@ -1344,12 +1344,12 @@
         <v>640505.15</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C55">
         <v>6</v>
@@ -1361,12 +1361,12 @@
         <v>720247.3</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C56" s="2">
         <v>7</v>
@@ -1378,12 +1378,12 @@
         <v>519238.50000000006</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C57" s="2">
         <v>8</v>
@@ -1395,12 +1395,12 @@
         <v>581947.30000000005</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C58" s="2">
         <v>9</v>
@@ -1412,12 +1412,12 @@
         <v>501345.9</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C59" s="2">
         <v>10</v>
@@ -1429,12 +1429,12 @@
         <v>515915.4</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C60" s="2">
         <v>11</v>
@@ -1446,12 +1446,12 @@
         <v>659208</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C61" s="2">
         <v>12</v>
@@ -1463,12 +1463,12 @@
         <v>441136.30000000005</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -1480,12 +1480,12 @@
         <v>460018.4</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -1497,12 +1497,12 @@
         <v>701240.1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C64">
         <v>3</v>
@@ -1514,12 +1514,12 @@
         <v>761615.1</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C65">
         <v>4</v>
@@ -1531,12 +1531,12 @@
         <v>562320.1</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C66">
         <v>5</v>
@@ -1548,12 +1548,12 @@
         <v>729120.7</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C67">
         <v>6</v>
@@ -1565,12 +1565,12 @@
         <v>872906.35</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C68" s="2">
         <v>7</v>
@@ -1582,12 +1582,12 @@
         <v>623986</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C69" s="2">
         <v>8</v>
@@ -1599,12 +1599,12 @@
         <v>831565.9</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C70" s="2">
         <v>9</v>
@@ -1616,12 +1616,12 @@
         <v>857622.70000000007</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C71" s="2">
         <v>10</v>
@@ -1633,12 +1633,12 @@
         <v>635996.9</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C72" s="2">
         <v>11</v>
@@ -1650,12 +1650,12 @@
         <v>822134.50000000012</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C73" s="2">
         <v>12</v>
@@ -1667,12 +1667,12 @@
         <v>661690.70000000007</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -1684,12 +1684,12 @@
         <v>483127.65</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -1701,12 +1701,12 @@
         <v>707742.2</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C76">
         <v>3</v>
@@ -1718,12 +1718,12 @@
         <v>924192.9</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C77">
         <v>4</v>
@@ -1735,12 +1735,12 @@
         <v>648338.94999999995</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C78">
         <v>5</v>
@@ -1752,12 +1752,12 @@
         <v>709702.95</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C79">
         <v>6</v>
@@ -1769,12 +1769,12 @@
         <v>819977.6</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C80" s="2">
         <v>7</v>
@@ -1786,12 +1786,12 @@
         <v>600272.20000000007</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C81" s="2">
         <v>8</v>
@@ -1803,12 +1803,12 @@
         <v>796998.4</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C82" s="2">
         <v>9</v>
@@ -1820,12 +1820,12 @@
         <v>626132.10000000009</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C83" s="2">
         <v>10</v>
@@ -1837,12 +1837,12 @@
         <v>591717.5</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C84" s="2">
         <v>11</v>
@@ -1854,12 +1854,12 @@
         <v>791032.00000000012</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C85" s="2">
         <v>12</v>
@@ -1871,12 +1871,12 @@
         <v>661831.5</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -1888,12 +1888,12 @@
         <v>444077.1</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C87">
         <v>2</v>
@@ -1905,12 +1905,12 @@
         <v>565701.1</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C88">
         <v>3</v>
@@ -1922,12 +1922,12 @@
         <v>699833.65</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C89">
         <v>4</v>
@@ -1939,12 +1939,12 @@
         <v>578230.35</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C90">
         <v>5</v>
@@ -1956,12 +1956,12 @@
         <v>649040.44999999995</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C91">
         <v>6</v>
@@ -1973,12 +1973,12 @@
         <v>737522.6</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C92" s="2">
         <v>7</v>
@@ -1990,12 +1990,12 @@
         <v>562719.30000000005</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C93" s="2">
         <v>8</v>
@@ -2007,12 +2007,12 @@
         <v>780060.60000000009</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C94" s="2">
         <v>9</v>
@@ -2024,12 +2024,12 @@
         <v>606140.70000000007</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C95" s="2">
         <v>10</v>
@@ -2041,12 +2041,12 @@
         <v>603181.70000000007</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C96" s="2">
         <v>11</v>
@@ -2058,12 +2058,12 @@
         <v>708184.4</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C97" s="2">
         <v>12</v>
@@ -2075,12 +2075,12 @@
         <v>721743.00000000012</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -2092,12 +2092,12 @@
         <v>447132.4</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C99" s="2">
         <v>2</v>
@@ -2109,12 +2109,12 @@
         <v>583671</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C100" s="2">
         <v>3</v>
@@ -2126,12 +2126,12 @@
         <v>543246</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C101" s="2">
         <v>4</v>
@@ -2143,12 +2143,12 @@
         <v>420537.7</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C102" s="2">
         <v>5</v>
@@ -2160,12 +2160,12 @@
         <v>610426.30000000005</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C103" s="2">
         <v>6</v>
@@ -2177,12 +2177,12 @@
         <v>430988.80000000005</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
@@ -2194,12 +2194,12 @@
         <v>468160.00000000006</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C105" s="2">
         <v>2</v>
@@ -2211,12 +2211,12 @@
         <v>710494.4</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C106" s="2">
         <v>3</v>
@@ -2228,12 +2228,12 @@
         <v>734202.70000000007</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C107" s="2">
         <v>4</v>
@@ -2245,12 +2245,12 @@
         <v>533989.5</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C108" s="2">
         <v>5</v>
@@ -2262,12 +2262,12 @@
         <v>783138.4</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C109" s="2">
         <v>6</v>
@@ -2279,12 +2279,12 @@
         <v>632283.30000000005</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
@@ -2296,12 +2296,12 @@
         <v>420468.4</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C111" s="2">
         <v>2</v>
@@ -2313,12 +2313,12 @@
         <v>768489.70000000007</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C112" s="2">
         <v>3</v>
@@ -2330,12 +2330,12 @@
         <v>707430.9</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C113" s="2">
         <v>4</v>
@@ -2347,12 +2347,12 @@
         <v>548621.70000000007</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C114" s="2">
         <v>5</v>
@@ -2364,12 +2364,12 @@
         <v>628012</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C115" s="2">
         <v>6</v>
@@ -2381,12 +2381,12 @@
         <v>654494.5</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
@@ -2398,12 +2398,12 @@
         <v>408622.50000000006</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C117" s="2">
         <v>2</v>
@@ -2415,12 +2415,12 @@
         <v>710213.9</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C118" s="2">
         <v>3</v>
@@ -2432,12 +2432,12 @@
         <v>534640.70000000007</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C119" s="2">
         <v>4</v>
@@ -2449,12 +2449,12 @@
         <v>565877.4</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C120" s="2">
         <v>5</v>
@@ -2466,12 +2466,12 @@
         <v>699802.4</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C121" s="2">
         <v>6</v>
